--- a/docs/book-plan.xlsx
+++ b/docs/book-plan.xlsx
@@ -1296,14 +1296,14 @@
           <t>完成</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -1311,14 +1311,14 @@
           <t>完成</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>进行中</t>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>steps 已补;对话待真实材料</t>
+          <t>全部完成:steps✅ 对话✅(Kimi) Prompt✅(CH02-001) 习题✅</t>
         </is>
       </c>
     </row>
@@ -1990,9 +1990,9 @@
           <t>5 章 ≥5 篇</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>阻塞</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>铁律:对话必须真实,需作者提供原始记录</t>
+          <t>ch02 已开张(let-ai-write-env-check);ch01/03/04/05 待素材</t>
         </is>
       </c>
     </row>
@@ -2054,9 +2054,9 @@
           <t>ch06</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>进行中</t>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>已下载,跑脚本得值后填</t>
+          <t>已填 9.5MB/91edf86…,用户复跑一致</t>
         </is>
       </c>
     </row>
